--- a/note/tables.xlsx
+++ b/note/tables.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910DA017-86C6-4B6F-AD8A-2835AD445AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE29BF6-D5D2-4DCF-BFBC-6D7206A438A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="USERBASIS" sheetId="1" r:id="rId1"/>
     <sheet name="INQUIRIES" sheetId="7" r:id="rId2"/>
-    <sheet name="WALLET_LEDGER" sheetId="8" r:id="rId3"/>
-    <sheet name="WALANCES" sheetId="9" r:id="rId4"/>
+    <sheet name="WALANCES" sheetId="9" r:id="rId3"/>
+    <sheet name="WALLET_LEDGER" sheetId="8" r:id="rId4"/>
     <sheet name="ROLEBASIS" sheetId="2" r:id="rId5"/>
     <sheet name="USER_STATS" sheetId="3" r:id="rId6"/>
     <sheet name="BUSINESS_PAGES" sheetId="13" r:id="rId7"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="290">
   <si>
     <t>欄位名稱</t>
   </si>
@@ -1010,6 +1010,14 @@
   </si>
   <si>
     <t>CHAR(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可用餘額</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WALLET_BALANCES（餘額快取表）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2793,6 +2801,87 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20354BF-4F84-4E95-A339-0261BEB602AA}">
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2628166-061C-4CD1-8E17-220D45A512C7}">
   <dimension ref="B2:D12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2917,76 +3006,6 @@
       </c>
       <c r="D12" s="2" t="s">
         <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20354BF-4F84-4E95-A339-0261BEB602AA}">
-  <dimension ref="B2:D6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/note/tables.xlsx
+++ b/note/tables.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE29BF6-D5D2-4DCF-BFBC-6D7206A438A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98203A5-2FD8-4AB3-9E92-F90E22EF5550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="USERBASIS" sheetId="1" r:id="rId1"/>
-    <sheet name="INQUIRIES" sheetId="7" r:id="rId2"/>
-    <sheet name="WALANCES" sheetId="9" r:id="rId3"/>
-    <sheet name="WALLET_LEDGER" sheetId="8" r:id="rId4"/>
-    <sheet name="ROLEBASIS" sheetId="2" r:id="rId5"/>
-    <sheet name="USER_STATS" sheetId="3" r:id="rId6"/>
-    <sheet name="BUSINESS_PAGES" sheetId="13" r:id="rId7"/>
-    <sheet name="SERVICE" sheetId="4" r:id="rId8"/>
-    <sheet name="ORDERS" sheetId="5" r:id="rId9"/>
-    <sheet name="REVIEWS" sheetId="6" r:id="rId10"/>
-    <sheet name="工作表9" sheetId="10" r:id="rId11"/>
-    <sheet name="工作表10" sheetId="11" r:id="rId12"/>
+    <sheet name="工作表1" sheetId="14" r:id="rId2"/>
+    <sheet name="INQUIRIES" sheetId="7" r:id="rId3"/>
+    <sheet name="WALANCES" sheetId="9" r:id="rId4"/>
+    <sheet name="WALLET_LEDGER" sheetId="8" r:id="rId5"/>
+    <sheet name="ROLEBASIS" sheetId="2" r:id="rId6"/>
+    <sheet name="USER_STATS" sheetId="3" r:id="rId7"/>
+    <sheet name="BUSINESS_PAGES" sheetId="13" r:id="rId8"/>
+    <sheet name="SERVICE" sheetId="4" r:id="rId9"/>
+    <sheet name="ORDERS" sheetId="5" r:id="rId10"/>
+    <sheet name="REVIEWS" sheetId="6" r:id="rId11"/>
+    <sheet name="工作表9" sheetId="10" r:id="rId12"/>
+    <sheet name="工作表10" sheetId="11" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="395">
   <si>
     <t>欄位名稱</t>
   </si>
@@ -1019,6 +1020,333 @@
   <si>
     <t>WALLET_BALANCES（餘額快取表）</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>資料類型</t>
+  </si>
+  <si>
+    <t>身份</t>
+  </si>
+  <si>
+    <t>整理</t>
+  </si>
+  <si>
+    <t>不為空</t>
+  </si>
+  <si>
+    <t>預設</t>
+  </si>
+  <si>
+    <t>評論</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>uuid</t>
+  </si>
+  <si>
+    <t>[NULL]</t>
+  </si>
+  <si>
+    <t>gen_random_uuid()</t>
+  </si>
+  <si>
+    <t>avatar_url</t>
+  </si>
+  <si>
+    <t>varchar(512)</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>使用者圖像 URL</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>varchar(254)</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>varchar(32)</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>varchar(80)</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>bpchar(1)</t>
+  </si>
+  <si>
+    <t>'N'::bpchar</t>
+  </si>
+  <si>
+    <t>birthdate</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>last_seen_at</t>
+  </si>
+  <si>
+    <t>timestamptz</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>now()</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>varchar(100)</t>
+  </si>
+  <si>
+    <t>address_no</t>
+  </si>
+  <si>
+    <t>登入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_basis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>達人註冊問卷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeABoss.cshtml</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossServices</t>
+  </si>
+  <si>
+    <t>Auth</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accoun</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackController</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontController</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetCategories</t>
+  </si>
+  <si>
+    <t>三層服務項目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>service_category</t>
+  </si>
+  <si>
+    <t>service_subcategory</t>
+  </si>
+  <si>
+    <t>service_item</t>
+  </si>
+  <si>
+    <t>category_id</t>
+  </si>
+  <si>
+    <t>服務大分類ID (PK)</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>大分類名稱</t>
+  </si>
+  <si>
+    <t>sort_order</t>
+  </si>
+  <si>
+    <t>int4</t>
+  </si>
+  <si>
+    <t>排序用數值，數字越小顯示越前面</t>
+  </si>
+  <si>
+    <t>subcategory_id</t>
+  </si>
+  <si>
+    <t>服務中分類ID (PK)</t>
+  </si>
+  <si>
+    <t>對應的服務大分類ID (FK)</t>
+  </si>
+  <si>
+    <t>中分類名稱</t>
+  </si>
+  <si>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>服務項目ID (PK)</t>
+  </si>
+  <si>
+    <t>對應的服務中分類ID (FK)</t>
+  </si>
+  <si>
+    <t>具體服務項目名稱</t>
+  </si>
+  <si>
+    <t>城市區域</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>GetCities</t>
+  </si>
+  <si>
+    <t>GetDistricts</t>
+  </si>
+  <si>
+    <t>location_city</t>
+  </si>
+  <si>
+    <t>location_district</t>
+  </si>
+  <si>
+    <t>city_id</t>
+  </si>
+  <si>
+    <t>serial4</t>
+  </si>
+  <si>
+    <t>nextval('location_city_city_id_seq'::regclass)</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>city_name</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>varchar(20)</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>numeric(9, 6)</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>district_id</t>
+  </si>
+  <si>
+    <t>nextval('location_district_district_id_seq'::regclass)</t>
+  </si>
+  <si>
+    <t>district_name</t>
+  </si>
+  <si>
+    <t>送出</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossServiceQuestionnaire</t>
+  </si>
+  <si>
+    <t>Submit</t>
+  </si>
+  <si>
+    <t>BossServiceRepo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReplaceItemsAsync</t>
+  </si>
+  <si>
+    <t>ReplaceMethodsAsync</t>
+  </si>
+  <si>
+    <t>ReplaceAreasAsync</t>
+  </si>
+  <si>
+    <t>ReplaceAddressesAsync</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>min_price</t>
+  </si>
+  <si>
+    <t>max_price</t>
+  </si>
+  <si>
+    <t>boss_service_item</t>
+  </si>
+  <si>
+    <t>boss_service_method</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>boss_service_area</t>
+  </si>
+  <si>
+    <t>boss_service_address</t>
   </si>
 </sst>
 </file>
@@ -1075,12 +1403,42 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1095,7 +1453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1130,6 +1488,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1601,11 +1980,11 @@
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
@@ -1617,13 +1996,13 @@
       <c r="D13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="G13" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1637,24 +2016,24 @@
       <c r="D14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="14" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="14" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1664,13 +2043,13 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="14" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1684,13 +2063,13 @@
       <c r="D17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="14" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1704,13 +2083,13 @@
       <c r="D18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="14" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1724,13 +2103,13 @@
       <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="14" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1744,13 +2123,13 @@
       <c r="D20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="14" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1764,13 +2143,13 @@
       <c r="D21" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="14" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1784,13 +2163,13 @@
       <c r="D22" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1804,6 +2183,9 @@
       <c r="D23" s="2" t="s">
         <v>205</v>
       </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
@@ -1815,6 +2197,9 @@
       <c r="D24" s="2" t="s">
         <v>207</v>
       </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
@@ -1826,11 +2211,11 @@
       <c r="D25" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
@@ -1842,13 +2227,13 @@
       <c r="D26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="G26" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1862,13 +2247,13 @@
       <c r="D27" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="17" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1882,13 +2267,13 @@
       <c r="D28" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="17" t="s">
         <v>126</v>
       </c>
     </row>
@@ -1902,13 +2287,13 @@
       <c r="D29" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="17" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1971,6 +2356,164 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0814FF0-F9D2-41F6-B002-E53DB7A15AE1}">
+  <dimension ref="B3:D16"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9AA739-6680-46B4-9024-B72EE3209FB0}">
   <dimension ref="B2:D11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2084,7 +2627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3FF41-02B8-48C6-80AC-8B997D914EEC}">
   <dimension ref="B2:D18"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2275,7 +2818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FCE46E1-DABE-4AD0-B68F-6850E7F80D52}">
   <dimension ref="B2:D6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2335,6 +2878,1974 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E3A6C1-8929-486D-B0BE-3540CE97F9A0}">
+  <dimension ref="A2:N75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="14" max="14" width="40.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L2" t="s">
+        <v>295</v>
+      </c>
+      <c r="M2" t="s">
+        <v>296</v>
+      </c>
+      <c r="N2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>299</v>
+      </c>
+      <c r="J3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>301</v>
+      </c>
+      <c r="N3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G4" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>303</v>
+      </c>
+      <c r="J4" t="s">
+        <v>300</v>
+      </c>
+      <c r="K4" t="s">
+        <v>304</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>300</v>
+      </c>
+      <c r="N4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G5" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>307</v>
+      </c>
+      <c r="J5" t="s">
+        <v>300</v>
+      </c>
+      <c r="K5" t="s">
+        <v>304</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>300</v>
+      </c>
+      <c r="N5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>308</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>309</v>
+      </c>
+      <c r="J6" t="s">
+        <v>300</v>
+      </c>
+      <c r="K6" t="s">
+        <v>304</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>300</v>
+      </c>
+      <c r="N6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>311</v>
+      </c>
+      <c r="J7" t="s">
+        <v>300</v>
+      </c>
+      <c r="K7" t="s">
+        <v>304</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>300</v>
+      </c>
+      <c r="N7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>313</v>
+      </c>
+      <c r="J8" t="s">
+        <v>300</v>
+      </c>
+      <c r="K8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>314</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>315</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9" t="s">
+        <v>316</v>
+      </c>
+      <c r="J9" t="s">
+        <v>300</v>
+      </c>
+      <c r="K9" t="s">
+        <v>300</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>300</v>
+      </c>
+      <c r="N9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G10" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>318</v>
+      </c>
+      <c r="J10" t="s">
+        <v>300</v>
+      </c>
+      <c r="K10" t="s">
+        <v>300</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11" t="s">
+        <v>320</v>
+      </c>
+      <c r="J11" t="s">
+        <v>300</v>
+      </c>
+      <c r="K11" t="s">
+        <v>300</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>300</v>
+      </c>
+      <c r="N11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G12" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>320</v>
+      </c>
+      <c r="J12" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" t="s">
+        <v>300</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>322</v>
+      </c>
+      <c r="N12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13" t="s">
+        <v>320</v>
+      </c>
+      <c r="J13" t="s">
+        <v>300</v>
+      </c>
+      <c r="K13" t="s">
+        <v>300</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>322</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>324</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
+      </c>
+      <c r="I14" t="s">
+        <v>325</v>
+      </c>
+      <c r="J14" t="s">
+        <v>300</v>
+      </c>
+      <c r="K14" t="s">
+        <v>304</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>300</v>
+      </c>
+      <c r="N14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>326</v>
+      </c>
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="I15" t="s">
+        <v>325</v>
+      </c>
+      <c r="J15" t="s">
+        <v>300</v>
+      </c>
+      <c r="K15" t="s">
+        <v>304</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>300</v>
+      </c>
+      <c r="N15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16" t="s">
+        <v>328</v>
+      </c>
+      <c r="J16" t="s">
+        <v>300</v>
+      </c>
+      <c r="K16" t="s">
+        <v>304</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>300</v>
+      </c>
+      <c r="N16" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>329</v>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>325</v>
+      </c>
+      <c r="J17" t="s">
+        <v>300</v>
+      </c>
+      <c r="K17" t="s">
+        <v>304</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>300</v>
+      </c>
+      <c r="N17" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" t="s">
+        <v>334</v>
+      </c>
+      <c r="F20" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" t="s">
+        <v>290</v>
+      </c>
+      <c r="H20" t="s">
+        <v>291</v>
+      </c>
+      <c r="I20" t="s">
+        <v>292</v>
+      </c>
+      <c r="J20" t="s">
+        <v>293</v>
+      </c>
+      <c r="K20" t="s">
+        <v>294</v>
+      </c>
+      <c r="L20" t="s">
+        <v>295</v>
+      </c>
+      <c r="M20" t="s">
+        <v>296</v>
+      </c>
+      <c r="N20" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" t="s">
+        <v>339</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>299</v>
+      </c>
+      <c r="J21" t="s">
+        <v>300</v>
+      </c>
+      <c r="K21" t="s">
+        <v>300</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>301</v>
+      </c>
+      <c r="N21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G22" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>325</v>
+      </c>
+      <c r="J22" t="s">
+        <v>300</v>
+      </c>
+      <c r="K22" t="s">
+        <v>304</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>300</v>
+      </c>
+      <c r="N22" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>348</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23" t="s">
+        <v>349</v>
+      </c>
+      <c r="J23" t="s">
+        <v>300</v>
+      </c>
+      <c r="K23" t="s">
+        <v>300</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>342</v>
+      </c>
+      <c r="G24" t="s">
+        <v>290</v>
+      </c>
+      <c r="H24" t="s">
+        <v>291</v>
+      </c>
+      <c r="I24" t="s">
+        <v>292</v>
+      </c>
+      <c r="J24" t="s">
+        <v>293</v>
+      </c>
+      <c r="K24" t="s">
+        <v>294</v>
+      </c>
+      <c r="L24" t="s">
+        <v>295</v>
+      </c>
+      <c r="M24" t="s">
+        <v>296</v>
+      </c>
+      <c r="N24" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G25" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>299</v>
+      </c>
+      <c r="J25" t="s">
+        <v>300</v>
+      </c>
+      <c r="K25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>301</v>
+      </c>
+      <c r="N25" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G26" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>299</v>
+      </c>
+      <c r="J26" t="s">
+        <v>300</v>
+      </c>
+      <c r="K26" t="s">
+        <v>300</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>300</v>
+      </c>
+      <c r="N26" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G27" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27" t="s">
+        <v>328</v>
+      </c>
+      <c r="J27" t="s">
+        <v>300</v>
+      </c>
+      <c r="K27" t="s">
+        <v>304</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>300</v>
+      </c>
+      <c r="N27" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>348</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28" t="s">
+        <v>349</v>
+      </c>
+      <c r="J28" t="s">
+        <v>300</v>
+      </c>
+      <c r="K28" t="s">
+        <v>300</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F29" t="s">
+        <v>343</v>
+      </c>
+      <c r="G29" t="s">
+        <v>290</v>
+      </c>
+      <c r="H29" t="s">
+        <v>291</v>
+      </c>
+      <c r="I29" t="s">
+        <v>292</v>
+      </c>
+      <c r="J29" t="s">
+        <v>293</v>
+      </c>
+      <c r="K29" t="s">
+        <v>294</v>
+      </c>
+      <c r="L29" t="s">
+        <v>295</v>
+      </c>
+      <c r="M29" t="s">
+        <v>296</v>
+      </c>
+      <c r="N29" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G30" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>299</v>
+      </c>
+      <c r="J30" t="s">
+        <v>300</v>
+      </c>
+      <c r="K30" t="s">
+        <v>300</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>301</v>
+      </c>
+      <c r="N30" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G31" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>299</v>
+      </c>
+      <c r="J31" t="s">
+        <v>300</v>
+      </c>
+      <c r="K31" t="s">
+        <v>300</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>300</v>
+      </c>
+      <c r="N31" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G32" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32" t="s">
+        <v>328</v>
+      </c>
+      <c r="J32" t="s">
+        <v>300</v>
+      </c>
+      <c r="K32" t="s">
+        <v>304</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>300</v>
+      </c>
+      <c r="N32" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>348</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="I33" t="s">
+        <v>349</v>
+      </c>
+      <c r="J33" t="s">
+        <v>300</v>
+      </c>
+      <c r="K33" t="s">
+        <v>300</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C35" t="s">
+        <v>360</v>
+      </c>
+      <c r="F35" t="s">
+        <v>363</v>
+      </c>
+      <c r="G35" t="s">
+        <v>290</v>
+      </c>
+      <c r="H35" t="s">
+        <v>291</v>
+      </c>
+      <c r="I35" t="s">
+        <v>292</v>
+      </c>
+      <c r="J35" t="s">
+        <v>293</v>
+      </c>
+      <c r="K35" t="s">
+        <v>294</v>
+      </c>
+      <c r="L35" t="s">
+        <v>295</v>
+      </c>
+      <c r="M35" t="s">
+        <v>296</v>
+      </c>
+      <c r="N35" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>361</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>366</v>
+      </c>
+      <c r="J36" t="s">
+        <v>300</v>
+      </c>
+      <c r="K36" t="s">
+        <v>300</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>367</v>
+      </c>
+      <c r="N36" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>362</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+      <c r="I37" t="s">
+        <v>325</v>
+      </c>
+      <c r="J37" t="s">
+        <v>300</v>
+      </c>
+      <c r="K37" t="s">
+        <v>304</v>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>300</v>
+      </c>
+      <c r="N37" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G38" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38" t="s">
+        <v>325</v>
+      </c>
+      <c r="J38" t="s">
+        <v>300</v>
+      </c>
+      <c r="K38" t="s">
+        <v>304</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>300</v>
+      </c>
+      <c r="N38" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>370</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="I39" t="s">
+        <v>371</v>
+      </c>
+      <c r="J39" t="s">
+        <v>300</v>
+      </c>
+      <c r="K39" t="s">
+        <v>304</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="s">
+        <v>300</v>
+      </c>
+      <c r="N39" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>372</v>
+      </c>
+      <c r="H40">
+        <v>5</v>
+      </c>
+      <c r="I40" t="s">
+        <v>373</v>
+      </c>
+      <c r="J40" t="s">
+        <v>300</v>
+      </c>
+      <c r="K40" t="s">
+        <v>300</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="s">
+        <v>300</v>
+      </c>
+      <c r="N40" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>374</v>
+      </c>
+      <c r="H41">
+        <v>6</v>
+      </c>
+      <c r="I41" t="s">
+        <v>373</v>
+      </c>
+      <c r="J41" t="s">
+        <v>300</v>
+      </c>
+      <c r="K41" t="s">
+        <v>300</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>300</v>
+      </c>
+      <c r="N41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>364</v>
+      </c>
+      <c r="G42" t="s">
+        <v>290</v>
+      </c>
+      <c r="H42" t="s">
+        <v>291</v>
+      </c>
+      <c r="I42" t="s">
+        <v>292</v>
+      </c>
+      <c r="J42" t="s">
+        <v>293</v>
+      </c>
+      <c r="K42" t="s">
+        <v>294</v>
+      </c>
+      <c r="L42" t="s">
+        <v>295</v>
+      </c>
+      <c r="M42" t="s">
+        <v>296</v>
+      </c>
+      <c r="N42" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G43" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>366</v>
+      </c>
+      <c r="J43" t="s">
+        <v>300</v>
+      </c>
+      <c r="K43" t="s">
+        <v>300</v>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>376</v>
+      </c>
+      <c r="N43" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G44" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>349</v>
+      </c>
+      <c r="J44" t="s">
+        <v>300</v>
+      </c>
+      <c r="K44" t="s">
+        <v>300</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="s">
+        <v>300</v>
+      </c>
+      <c r="N44" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G45" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+      <c r="I45" t="s">
+        <v>325</v>
+      </c>
+      <c r="J45" t="s">
+        <v>300</v>
+      </c>
+      <c r="K45" t="s">
+        <v>304</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
+        <v>300</v>
+      </c>
+      <c r="N45" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>370</v>
+      </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>371</v>
+      </c>
+      <c r="J46" t="s">
+        <v>300</v>
+      </c>
+      <c r="K46" t="s">
+        <v>304</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>300</v>
+      </c>
+      <c r="N46" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G47" t="s">
+        <v>372</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47" t="s">
+        <v>373</v>
+      </c>
+      <c r="J47" t="s">
+        <v>300</v>
+      </c>
+      <c r="K47" t="s">
+        <v>300</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>300</v>
+      </c>
+      <c r="N47" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>374</v>
+      </c>
+      <c r="H48">
+        <v>6</v>
+      </c>
+      <c r="I48" t="s">
+        <v>373</v>
+      </c>
+      <c r="J48" t="s">
+        <v>300</v>
+      </c>
+      <c r="K48" t="s">
+        <v>300</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
+        <v>300</v>
+      </c>
+      <c r="N48" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="C49" t="s">
+        <v>379</v>
+      </c>
+      <c r="D49" t="s">
+        <v>381</v>
+      </c>
+      <c r="E49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F49" t="s">
+        <v>389</v>
+      </c>
+      <c r="G49" t="s">
+        <v>290</v>
+      </c>
+      <c r="H49" t="s">
+        <v>291</v>
+      </c>
+      <c r="I49" t="s">
+        <v>292</v>
+      </c>
+      <c r="J49" t="s">
+        <v>293</v>
+      </c>
+      <c r="K49" t="s">
+        <v>294</v>
+      </c>
+      <c r="L49" t="s">
+        <v>295</v>
+      </c>
+      <c r="M49" t="s">
+        <v>296</v>
+      </c>
+      <c r="N49" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>380</v>
+      </c>
+      <c r="G50" t="s">
+        <v>386</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>299</v>
+      </c>
+      <c r="J50" t="s">
+        <v>300</v>
+      </c>
+      <c r="K50" t="s">
+        <v>300</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>301</v>
+      </c>
+      <c r="N50" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>298</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+      <c r="I51" t="s">
+        <v>299</v>
+      </c>
+      <c r="J51" t="s">
+        <v>300</v>
+      </c>
+      <c r="K51" t="s">
+        <v>300</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>300</v>
+      </c>
+      <c r="N51" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>355</v>
+      </c>
+      <c r="H52">
+        <v>3</v>
+      </c>
+      <c r="I52" t="s">
+        <v>299</v>
+      </c>
+      <c r="J52" t="s">
+        <v>300</v>
+      </c>
+      <c r="K52" t="s">
+        <v>300</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="s">
+        <v>300</v>
+      </c>
+      <c r="N52" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>321</v>
+      </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53" t="s">
+        <v>320</v>
+      </c>
+      <c r="J53" t="s">
+        <v>300</v>
+      </c>
+      <c r="K53" t="s">
+        <v>300</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>322</v>
+      </c>
+      <c r="N53" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>387</v>
+      </c>
+      <c r="H54">
+        <v>5</v>
+      </c>
+      <c r="I54" t="s">
+        <v>349</v>
+      </c>
+      <c r="J54" t="s">
+        <v>300</v>
+      </c>
+      <c r="K54" t="s">
+        <v>300</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>388</v>
+      </c>
+      <c r="H55">
+        <v>6</v>
+      </c>
+      <c r="I55" t="s">
+        <v>349</v>
+      </c>
+      <c r="J55" t="s">
+        <v>300</v>
+      </c>
+      <c r="K55" t="s">
+        <v>300</v>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E56" t="s">
+        <v>383</v>
+      </c>
+      <c r="F56" t="s">
+        <v>390</v>
+      </c>
+      <c r="G56" t="s">
+        <v>290</v>
+      </c>
+      <c r="H56" t="s">
+        <v>291</v>
+      </c>
+      <c r="I56" t="s">
+        <v>292</v>
+      </c>
+      <c r="J56" t="s">
+        <v>293</v>
+      </c>
+      <c r="K56" t="s">
+        <v>294</v>
+      </c>
+      <c r="L56" t="s">
+        <v>295</v>
+      </c>
+      <c r="M56" t="s">
+        <v>296</v>
+      </c>
+      <c r="N56" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>386</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>299</v>
+      </c>
+      <c r="J57" t="s">
+        <v>300</v>
+      </c>
+      <c r="K57" t="s">
+        <v>300</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" t="s">
+        <v>301</v>
+      </c>
+      <c r="N57" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>298</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+      <c r="I58" t="s">
+        <v>299</v>
+      </c>
+      <c r="J58" t="s">
+        <v>300</v>
+      </c>
+      <c r="K58" t="s">
+        <v>300</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="s">
+        <v>300</v>
+      </c>
+      <c r="N58" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>391</v>
+      </c>
+      <c r="H59">
+        <v>3</v>
+      </c>
+      <c r="I59" t="s">
+        <v>392</v>
+      </c>
+      <c r="J59" t="s">
+        <v>300</v>
+      </c>
+      <c r="K59" t="s">
+        <v>304</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+      <c r="M59" t="s">
+        <v>300</v>
+      </c>
+      <c r="N59" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>323</v>
+      </c>
+      <c r="H60">
+        <v>4</v>
+      </c>
+      <c r="I60" t="s">
+        <v>320</v>
+      </c>
+      <c r="J60" t="s">
+        <v>300</v>
+      </c>
+      <c r="K60" t="s">
+        <v>300</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" t="s">
+        <v>322</v>
+      </c>
+      <c r="N60" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E61" t="s">
+        <v>384</v>
+      </c>
+      <c r="F61" t="s">
+        <v>393</v>
+      </c>
+      <c r="G61" t="s">
+        <v>290</v>
+      </c>
+      <c r="H61" t="s">
+        <v>291</v>
+      </c>
+      <c r="I61" t="s">
+        <v>292</v>
+      </c>
+      <c r="J61" t="s">
+        <v>293</v>
+      </c>
+      <c r="K61" t="s">
+        <v>294</v>
+      </c>
+      <c r="L61" t="s">
+        <v>295</v>
+      </c>
+      <c r="M61" t="s">
+        <v>296</v>
+      </c>
+      <c r="N61" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>386</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>299</v>
+      </c>
+      <c r="J62" t="s">
+        <v>300</v>
+      </c>
+      <c r="K62" t="s">
+        <v>300</v>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
+      <c r="M62" t="s">
+        <v>301</v>
+      </c>
+      <c r="N62" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>298</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63" t="s">
+        <v>299</v>
+      </c>
+      <c r="J63" t="s">
+        <v>300</v>
+      </c>
+      <c r="K63" t="s">
+        <v>300</v>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
+      <c r="M63" t="s">
+        <v>300</v>
+      </c>
+      <c r="N63" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>365</v>
+      </c>
+      <c r="H64">
+        <v>3</v>
+      </c>
+      <c r="I64" t="s">
+        <v>349</v>
+      </c>
+      <c r="J64" t="s">
+        <v>300</v>
+      </c>
+      <c r="K64" t="s">
+        <v>300</v>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
+      <c r="M64" t="s">
+        <v>300</v>
+      </c>
+      <c r="N64" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="65" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>375</v>
+      </c>
+      <c r="H65">
+        <v>4</v>
+      </c>
+      <c r="I65" t="s">
+        <v>349</v>
+      </c>
+      <c r="J65" t="s">
+        <v>300</v>
+      </c>
+      <c r="K65" t="s">
+        <v>300</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="s">
+        <v>300</v>
+      </c>
+      <c r="N65" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>321</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66" t="s">
+        <v>320</v>
+      </c>
+      <c r="J66" t="s">
+        <v>300</v>
+      </c>
+      <c r="K66" t="s">
+        <v>300</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="s">
+        <v>322</v>
+      </c>
+      <c r="N66" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E67" t="s">
+        <v>385</v>
+      </c>
+      <c r="F67" t="s">
+        <v>394</v>
+      </c>
+      <c r="G67" t="s">
+        <v>290</v>
+      </c>
+      <c r="H67" t="s">
+        <v>291</v>
+      </c>
+      <c r="I67" t="s">
+        <v>292</v>
+      </c>
+      <c r="J67" t="s">
+        <v>293</v>
+      </c>
+      <c r="K67" t="s">
+        <v>294</v>
+      </c>
+      <c r="L67" t="s">
+        <v>295</v>
+      </c>
+      <c r="M67" t="s">
+        <v>296</v>
+      </c>
+      <c r="N67" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="68" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>386</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>299</v>
+      </c>
+      <c r="J68" t="s">
+        <v>300</v>
+      </c>
+      <c r="K68" t="s">
+        <v>300</v>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>301</v>
+      </c>
+      <c r="N68" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>298</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
+        <v>299</v>
+      </c>
+      <c r="J69" t="s">
+        <v>300</v>
+      </c>
+      <c r="K69" t="s">
+        <v>300</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="s">
+        <v>300</v>
+      </c>
+      <c r="N69" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>365</v>
+      </c>
+      <c r="H70">
+        <v>3</v>
+      </c>
+      <c r="I70" t="s">
+        <v>349</v>
+      </c>
+      <c r="J70" t="s">
+        <v>300</v>
+      </c>
+      <c r="K70" t="s">
+        <v>300</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="s">
+        <v>300</v>
+      </c>
+      <c r="N70" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G71" t="s">
+        <v>375</v>
+      </c>
+      <c r="H71">
+        <v>4</v>
+      </c>
+      <c r="I71" t="s">
+        <v>349</v>
+      </c>
+      <c r="J71" t="s">
+        <v>300</v>
+      </c>
+      <c r="K71" t="s">
+        <v>300</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="s">
+        <v>300</v>
+      </c>
+      <c r="N71" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="72" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G72" t="s">
+        <v>327</v>
+      </c>
+      <c r="H72">
+        <v>5</v>
+      </c>
+      <c r="I72" t="s">
+        <v>328</v>
+      </c>
+      <c r="J72" t="s">
+        <v>300</v>
+      </c>
+      <c r="K72" t="s">
+        <v>304</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="s">
+        <v>300</v>
+      </c>
+      <c r="N72" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="73" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G73" t="s">
+        <v>329</v>
+      </c>
+      <c r="H73">
+        <v>6</v>
+      </c>
+      <c r="I73" t="s">
+        <v>325</v>
+      </c>
+      <c r="J73" t="s">
+        <v>300</v>
+      </c>
+      <c r="K73" t="s">
+        <v>304</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="s">
+        <v>300</v>
+      </c>
+      <c r="N73" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>321</v>
+      </c>
+      <c r="H74">
+        <v>7</v>
+      </c>
+      <c r="I74" t="s">
+        <v>320</v>
+      </c>
+      <c r="J74" t="s">
+        <v>300</v>
+      </c>
+      <c r="K74" t="s">
+        <v>300</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="s">
+        <v>322</v>
+      </c>
+      <c r="N74" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="75" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="G75" t="s">
+        <v>323</v>
+      </c>
+      <c r="H75">
+        <v>8</v>
+      </c>
+      <c r="I75" t="s">
+        <v>320</v>
+      </c>
+      <c r="J75" t="s">
+        <v>300</v>
+      </c>
+      <c r="K75" t="s">
+        <v>300</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="s">
+        <v>322</v>
+      </c>
+      <c r="N75" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0748038D-1236-4988-927E-F84C4BE6FB57}">
   <dimension ref="B2:H25"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2800,7 +5311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20354BF-4F84-4E95-A339-0261BEB602AA}">
   <dimension ref="B2:D7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2881,7 +5392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2628166-061C-4CD1-8E17-220D45A512C7}">
   <dimension ref="B2:D12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3017,7 +5528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB157D-DAD5-4469-B47A-8F1B8BB5E87F}">
   <dimension ref="B2:D10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3117,7 +5628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1B5E7C-69C2-4771-ACE8-8F429CDFDDC0}">
   <dimension ref="B2:D19"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3330,7 +5841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC1774E-773F-4BF5-B419-73A866990E01}">
   <dimension ref="B2:D31"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3617,7 +6128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E56573-585C-4CF5-B8A4-057305F06120}">
   <dimension ref="B2:D23"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -3825,162 +6336,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0814FF0-F9D2-41F6-B002-E53DB7A15AE1}">
-  <dimension ref="B3:D16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:D3"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/note/tables.xlsx
+++ b/note/tables.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98203A5-2FD8-4AB3-9E92-F90E22EF5550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0916B686-C30C-47C3-B946-D7B00D5A0967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="USERBASIS" sheetId="1" r:id="rId1"/>
     <sheet name="工作表1" sheetId="14" r:id="rId2"/>
-    <sheet name="INQUIRIES" sheetId="7" r:id="rId3"/>
-    <sheet name="WALANCES" sheetId="9" r:id="rId4"/>
-    <sheet name="WALLET_LEDGER" sheetId="8" r:id="rId5"/>
-    <sheet name="ROLEBASIS" sheetId="2" r:id="rId6"/>
-    <sheet name="USER_STATS" sheetId="3" r:id="rId7"/>
-    <sheet name="BUSINESS_PAGES" sheetId="13" r:id="rId8"/>
-    <sheet name="SERVICE" sheetId="4" r:id="rId9"/>
-    <sheet name="ORDERS" sheetId="5" r:id="rId10"/>
-    <sheet name="REVIEWS" sheetId="6" r:id="rId11"/>
-    <sheet name="工作表9" sheetId="10" r:id="rId12"/>
-    <sheet name="工作表10" sheetId="11" r:id="rId13"/>
+    <sheet name="工作表2" sheetId="15" r:id="rId3"/>
+    <sheet name="INQUIRIES" sheetId="7" r:id="rId4"/>
+    <sheet name="WALANCES" sheetId="9" r:id="rId5"/>
+    <sheet name="WALLET_LEDGER" sheetId="8" r:id="rId6"/>
+    <sheet name="ROLEBASIS" sheetId="2" r:id="rId7"/>
+    <sheet name="USER_STATS" sheetId="3" r:id="rId8"/>
+    <sheet name="BUSINESS_PAGES" sheetId="13" r:id="rId9"/>
+    <sheet name="SERVICE" sheetId="4" r:id="rId10"/>
+    <sheet name="ORDERS" sheetId="5" r:id="rId11"/>
+    <sheet name="REVIEWS" sheetId="6" r:id="rId12"/>
+    <sheet name="工作表9" sheetId="10" r:id="rId13"/>
+    <sheet name="工作表10" sheetId="11" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="434">
   <si>
     <t>欄位名稱</t>
   </si>
@@ -1031,12 +1032,6 @@
     <t>資料類型</t>
   </si>
   <si>
-    <t>身份</t>
-  </si>
-  <si>
-    <t>整理</t>
-  </si>
-  <si>
     <t>不為空</t>
   </si>
   <si>
@@ -1062,9 +1057,6 @@
   </si>
   <si>
     <t>varchar(512)</t>
-  </si>
-  <si>
-    <t>default</t>
   </si>
   <si>
     <t>使用者圖像 URL</t>
@@ -1347,6 +1339,140 @@
   </si>
   <si>
     <t>boss_service_address</t>
+  </si>
+  <si>
+    <t>表名</t>
+  </si>
+  <si>
+    <t>WALLET_BALANCES</t>
+  </si>
+  <si>
+    <t>錢包餘額快取（每用戶×幣別一筆，可用餘額，單位=分）</t>
+  </si>
+  <si>
+    <t>WALLET_LEDGER</t>
+  </si>
+  <si>
+    <t>錢包流水帳（每一筆入出帳紀錄，單位=分）</t>
+  </si>
+  <si>
+    <t>customer_service_method</t>
+  </si>
+  <si>
+    <t>customer_service_request</t>
+  </si>
+  <si>
+    <t>listings</t>
+  </si>
+  <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t>訂單主檔：記錄買賣雙方的成交資訊</t>
+  </si>
+  <si>
+    <t>rating_dimension</t>
+  </si>
+  <si>
+    <t>評分維度字典</t>
+  </si>
+  <si>
+    <t>review_score_items</t>
+  </si>
+  <si>
+    <t>評價分項：一筆評價對多個維度的分數（1~5）</t>
+  </si>
+  <si>
+    <t>reviews</t>
+  </si>
+  <si>
+    <t>評價主檔：誰在什麼時候對誰評價（含文字評語）</t>
+  </si>
+  <si>
+    <t>service_categories</t>
+  </si>
+  <si>
+    <t>服務分類主檔：支援多層樹狀分類</t>
+  </si>
+  <si>
+    <t>服務大分類，例如居家、學習、活動、健康、商業、其他</t>
+  </si>
+  <si>
+    <t>具體服務項目，例如冷氣清洗、搬家清潔、洗衣機清洗</t>
+  </si>
+  <si>
+    <t>服務中分類，例如清潔環衛、室內裝潢、家電維修</t>
+  </si>
+  <si>
+    <t>services</t>
+  </si>
+  <si>
+    <t>服務項目主檔：商家上架的服務資訊</t>
+  </si>
+  <si>
+    <t>spatial_ref_sys</t>
+  </si>
+  <si>
+    <t>store_content</t>
+  </si>
+  <si>
+    <t>user_basis</t>
+  </si>
+  <si>
+    <t>使用者主檔</t>
+  </si>
+  <si>
+    <t>user_rating_stats_daily</t>
+  </si>
+  <si>
+    <t>每日評分彙總快取：USER × ROLE × DIM × DAY</t>
+  </si>
+  <si>
+    <t>zones</t>
+  </si>
+  <si>
+    <t>小老闆頁面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bossstorecontent</t>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>get</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>content_html</t>
+  </si>
+  <si>
+    <t>_CategoryTiles.cshtml</t>
+  </si>
+  <si>
+    <t>stat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetServiceStatsAsync</t>
+  </si>
+  <si>
+    <t>客戶查詢頁面(單一區）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶查詢頁面(多區域)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Store/itemID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Store/userID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1403,7 +1529,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1440,6 +1566,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1453,7 +1591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1473,6 +1611,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1488,27 +1646,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1801,16 +1940,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="F2" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="F2" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -1893,11 +2032,11 @@
       <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -1980,11 +2119,11 @@
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
@@ -1996,13 +2135,13 @@
       <c r="D13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13" t="s">
+      <c r="G13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2016,40 +2155,40 @@
       <c r="D14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="8" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="8" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="F16" s="14" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="F16" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2063,13 +2202,13 @@
       <c r="D17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="8" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2083,13 +2222,13 @@
       <c r="D18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="8" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2103,13 +2242,13 @@
       <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="8" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2123,13 +2262,13 @@
       <c r="D20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="8" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2143,13 +2282,13 @@
       <c r="D21" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="8" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2163,13 +2302,13 @@
       <c r="D22" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="8" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2183,9 +2322,9 @@
       <c r="D23" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
@@ -2197,9 +2336,9 @@
       <c r="D24" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
@@ -2211,11 +2350,11 @@
       <c r="D25" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
@@ -2227,13 +2366,13 @@
       <c r="D26" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="G26" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16" t="s">
+      <c r="G26" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2247,13 +2386,13 @@
       <c r="D27" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="11" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2267,13 +2406,13 @@
       <c r="D28" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="11" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2287,13 +2426,13 @@
       <c r="D29" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="11" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2356,6 +2495,216 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E56573-585C-4CF5-B8A4-057305F06120}">
+  <dimension ref="B2:D23"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B11:D11"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0814FF0-F9D2-41F6-B002-E53DB7A15AE1}">
   <dimension ref="B3:D16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2366,11 +2715,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -2513,7 +2862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9AA739-6680-46B4-9024-B72EE3209FB0}">
   <dimension ref="B2:D11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2524,11 +2873,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2627,7 +2976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3FF41-02B8-48C6-80AC-8B997D914EEC}">
   <dimension ref="B2:D18"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2638,11 +2987,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2818,7 +3167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FCE46E1-DABE-4AD0-B68F-6850E7F80D52}">
   <dimension ref="B2:D6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2829,11 +3178,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2879,32 +3228,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E3A6C1-8929-486D-B0BE-3540CE97F9A0}">
-  <dimension ref="A2:N75"/>
+  <dimension ref="A2:Q81"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.42578125" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="14" max="14" width="40.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="12" max="12" width="33.140625" customWidth="1"/>
+    <col min="13" max="13" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="17" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G2" t="s">
         <v>290</v>
@@ -2924,425 +3275,328 @@
       <c r="L2" t="s">
         <v>295</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="C3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="N2" t="s">
+      <c r="H3" s="23">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
         <v>299</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G4" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="K3" t="s">
-        <v>300</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="H4" s="23">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
         <v>301</v>
       </c>
-      <c r="N3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G4" s="18" t="s">
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>298</v>
+      </c>
+      <c r="L4" t="s">
         <v>302</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G5" s="12" t="s">
         <v>303</v>
-      </c>
-      <c r="J4" t="s">
-        <v>300</v>
-      </c>
-      <c r="K4" t="s">
-        <v>304</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>300</v>
-      </c>
-      <c r="N4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G5" s="18" t="s">
-        <v>306</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>307</v>
-      </c>
-      <c r="J5" t="s">
-        <v>300</v>
+        <v>304</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>304</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>300</v>
-      </c>
-      <c r="N5" t="s">
+        <v>298</v>
+      </c>
+      <c r="L5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6" t="s">
-        <v>309</v>
-      </c>
-      <c r="J6" t="s">
-        <v>300</v>
+        <v>306</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>304</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>300</v>
-      </c>
-      <c r="N6" t="s">
+        <v>298</v>
+      </c>
+      <c r="L6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
       <c r="I7" t="s">
-        <v>311</v>
-      </c>
-      <c r="J7" t="s">
-        <v>300</v>
+        <v>308</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>304</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="s">
-        <v>300</v>
-      </c>
-      <c r="N7" t="s">
+        <v>298</v>
+      </c>
+      <c r="L7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H8">
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>313</v>
-      </c>
-      <c r="J8" t="s">
-        <v>300</v>
+        <v>310</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>304</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>314</v>
-      </c>
-      <c r="N8" t="s">
+        <v>311</v>
+      </c>
+      <c r="L8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H9">
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>316</v>
-      </c>
-      <c r="J9" t="s">
-        <v>300</v>
+        <v>313</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>300</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>300</v>
-      </c>
-      <c r="N9" t="s">
+        <v>298</v>
+      </c>
+      <c r="L9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G10" s="18" t="s">
-        <v>317</v>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G10" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10" t="s">
-        <v>318</v>
-      </c>
-      <c r="J10" t="s">
-        <v>300</v>
-      </c>
-      <c r="K10" t="s">
-        <v>300</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
+        <v>315</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H11">
         <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>320</v>
-      </c>
-      <c r="J11" t="s">
-        <v>300</v>
+        <v>317</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>300</v>
-      </c>
-      <c r="L11" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>300</v>
-      </c>
-      <c r="N11" t="s">
+        <v>298</v>
+      </c>
+      <c r="L11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G12" s="18" t="s">
-        <v>321</v>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G12" s="12" t="s">
+        <v>318</v>
       </c>
       <c r="H12">
         <v>10</v>
       </c>
       <c r="I12" t="s">
+        <v>317</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>319</v>
+      </c>
+      <c r="L12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
         <v>320</v>
-      </c>
-      <c r="J12" t="s">
-        <v>300</v>
-      </c>
-      <c r="K12" t="s">
-        <v>300</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>322</v>
-      </c>
-      <c r="N12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>323</v>
       </c>
       <c r="H13">
         <v>11</v>
       </c>
       <c r="I13" t="s">
-        <v>320</v>
-      </c>
-      <c r="J13" t="s">
-        <v>300</v>
+        <v>317</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>300</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" t="s">
-        <v>322</v>
-      </c>
-      <c r="N13" t="s">
+        <v>319</v>
+      </c>
+      <c r="L13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H14">
         <v>12</v>
       </c>
       <c r="I14" t="s">
-        <v>325</v>
-      </c>
-      <c r="J14" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>304</v>
-      </c>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" t="s">
-        <v>300</v>
-      </c>
-      <c r="N14" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G15" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H15">
         <v>13</v>
       </c>
       <c r="I15" t="s">
-        <v>325</v>
-      </c>
-      <c r="J15" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>304</v>
-      </c>
-      <c r="L15" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" t="s">
-        <v>300</v>
-      </c>
-      <c r="N15" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G16" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H16">
         <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>328</v>
-      </c>
-      <c r="J16" t="s">
-        <v>300</v>
+        <v>325</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>304</v>
-      </c>
-      <c r="L16" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" t="s">
-        <v>300</v>
-      </c>
-      <c r="N16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H17">
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>325</v>
-      </c>
-      <c r="J17" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>304</v>
-      </c>
-      <c r="L17" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" t="s">
-        <v>300</v>
-      </c>
-      <c r="N17" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L17" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B20" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C20" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F20" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G20" t="s">
         <v>290</v>
@@ -3362,100 +3616,76 @@
       <c r="L20" t="s">
         <v>295</v>
       </c>
-      <c r="M20" t="s">
-        <v>296</v>
-      </c>
-      <c r="N20" t="s">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" t="s">
+        <v>336</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="C21" t="s">
-        <v>339</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
         <v>299</v>
       </c>
-      <c r="J21" t="s">
-        <v>300</v>
-      </c>
-      <c r="K21" t="s">
-        <v>300</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="s">
-        <v>301</v>
-      </c>
-      <c r="N21" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G22" s="20" t="s">
-        <v>346</v>
+      <c r="L21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G22" s="13" t="s">
+        <v>343</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>325</v>
-      </c>
-      <c r="J22" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>304</v>
-      </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" t="s">
-        <v>300</v>
-      </c>
-      <c r="N22" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L22" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H23">
         <v>3</v>
       </c>
       <c r="I23" t="s">
-        <v>349</v>
-      </c>
-      <c r="J23" t="s">
-        <v>300</v>
-      </c>
-      <c r="K23" t="s">
-        <v>300</v>
-      </c>
-      <c r="L23" t="b">
+        <v>346</v>
+      </c>
+      <c r="J23" t="b">
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="K23">
         <v>0</v>
       </c>
-      <c r="N23" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F24" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G24" t="s">
         <v>290</v>
@@ -3475,120 +3705,90 @@
       <c r="L24" t="s">
         <v>295</v>
       </c>
-      <c r="M24" t="s">
-        <v>296</v>
-      </c>
-      <c r="N24" t="s">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G25" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G25" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
         <v>299</v>
       </c>
-      <c r="J25" t="s">
-        <v>300</v>
-      </c>
-      <c r="K25" t="s">
-        <v>300</v>
-      </c>
-      <c r="L25" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" t="s">
-        <v>301</v>
-      </c>
-      <c r="N25" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G26" s="20" t="s">
-        <v>344</v>
+      <c r="L25" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G26" s="13" t="s">
+        <v>341</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
       <c r="I26" t="s">
-        <v>299</v>
-      </c>
-      <c r="J26" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>300</v>
-      </c>
-      <c r="L26" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
-        <v>300</v>
-      </c>
-      <c r="N26" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G27" s="20" t="s">
-        <v>346</v>
+        <v>298</v>
+      </c>
+      <c r="L26" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G27" s="13" t="s">
+        <v>343</v>
       </c>
       <c r="H27">
         <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>328</v>
-      </c>
-      <c r="J27" t="s">
-        <v>300</v>
+        <v>325</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>304</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" t="s">
-        <v>300</v>
-      </c>
-      <c r="N27" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L27" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H28">
         <v>4</v>
       </c>
       <c r="I28" t="s">
-        <v>349</v>
-      </c>
-      <c r="J28" t="s">
-        <v>300</v>
-      </c>
-      <c r="K28" t="s">
-        <v>300</v>
-      </c>
-      <c r="L28" t="b">
+        <v>346</v>
+      </c>
+      <c r="J28" t="b">
         <v>0</v>
       </c>
-      <c r="M28">
+      <c r="K28">
         <v>0</v>
       </c>
-      <c r="N28" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L28" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G29" t="s">
         <v>290</v>
@@ -3608,126 +3808,96 @@
       <c r="L29" t="s">
         <v>295</v>
       </c>
-      <c r="M29" t="s">
-        <v>296</v>
-      </c>
-      <c r="N29" t="s">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G30" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G30" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="s">
         <v>299</v>
       </c>
-      <c r="J30" t="s">
-        <v>300</v>
-      </c>
-      <c r="K30" t="s">
-        <v>300</v>
-      </c>
-      <c r="L30" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" t="s">
-        <v>301</v>
-      </c>
-      <c r="N30" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G31" s="20" t="s">
-        <v>351</v>
+      <c r="L30" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G31" s="13" t="s">
+        <v>348</v>
       </c>
       <c r="H31">
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>299</v>
-      </c>
-      <c r="J31" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>300</v>
-      </c>
-      <c r="L31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" t="s">
-        <v>300</v>
-      </c>
-      <c r="N31" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G32" s="20" t="s">
-        <v>346</v>
+        <v>298</v>
+      </c>
+      <c r="L31" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G32" s="13" t="s">
+        <v>343</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>328</v>
-      </c>
-      <c r="J32" t="s">
-        <v>300</v>
+        <v>325</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>304</v>
-      </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" t="s">
-        <v>300</v>
-      </c>
-      <c r="N32" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L32" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G33" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H33">
         <v>4</v>
       </c>
       <c r="I33" t="s">
-        <v>349</v>
-      </c>
-      <c r="J33" t="s">
-        <v>300</v>
-      </c>
-      <c r="K33" t="s">
-        <v>300</v>
-      </c>
-      <c r="L33" t="b">
+        <v>346</v>
+      </c>
+      <c r="J33" t="b">
         <v>0</v>
       </c>
-      <c r="M33">
+      <c r="K33">
         <v>0</v>
       </c>
-      <c r="N33" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>359</v>
+      <c r="L33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>356</v>
       </c>
       <c r="C35" t="s">
+        <v>357</v>
+      </c>
+      <c r="F35" t="s">
         <v>360</v>
-      </c>
-      <c r="F35" t="s">
-        <v>363</v>
       </c>
       <c r="G35" t="s">
         <v>290</v>
@@ -3747,178 +3917,139 @@
       <c r="L35" t="s">
         <v>295</v>
       </c>
-      <c r="M35" t="s">
-        <v>296</v>
-      </c>
-      <c r="N35" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>361</v>
-      </c>
-      <c r="G36" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>363</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
+        <v>364</v>
+      </c>
+      <c r="L36" t="s">
+        <v>298</v>
+      </c>
+      <c r="O36" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>359</v>
+      </c>
+      <c r="G37" s="14" t="s">
         <v>365</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>366</v>
-      </c>
-      <c r="J36" t="s">
-        <v>300</v>
-      </c>
-      <c r="K36" t="s">
-        <v>300</v>
-      </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" t="s">
-        <v>367</v>
-      </c>
-      <c r="N36" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C37" t="s">
-        <v>362</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>368</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>325</v>
-      </c>
-      <c r="J37" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>304</v>
-      </c>
-      <c r="L37" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" t="s">
-        <v>300</v>
-      </c>
-      <c r="N37" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G38" s="21" t="s">
-        <v>369</v>
+        <v>298</v>
+      </c>
+      <c r="L37" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G38" s="14" t="s">
+        <v>366</v>
       </c>
       <c r="H38">
         <v>3</v>
       </c>
       <c r="I38" t="s">
-        <v>325</v>
-      </c>
-      <c r="J38" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>304</v>
-      </c>
-      <c r="L38" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" t="s">
-        <v>300</v>
-      </c>
-      <c r="N38" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L38" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G39" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H39">
         <v>4</v>
       </c>
       <c r="I39" t="s">
-        <v>371</v>
-      </c>
-      <c r="J39" t="s">
-        <v>300</v>
+        <v>368</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>304</v>
-      </c>
-      <c r="L39" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" t="s">
-        <v>300</v>
-      </c>
-      <c r="N39" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L39" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G40" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H40">
         <v>5</v>
       </c>
       <c r="I40" t="s">
-        <v>373</v>
-      </c>
-      <c r="J40" t="s">
-        <v>300</v>
+        <v>370</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>300</v>
-      </c>
-      <c r="L40" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" t="s">
-        <v>300</v>
-      </c>
-      <c r="N40" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L40" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G41" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H41">
         <v>6</v>
       </c>
       <c r="I41" t="s">
-        <v>373</v>
-      </c>
-      <c r="J41" t="s">
-        <v>300</v>
+        <v>370</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>300</v>
-      </c>
-      <c r="L41" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" t="s">
-        <v>300</v>
-      </c>
-      <c r="N41" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L41" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F42" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G42" t="s">
         <v>290</v>
@@ -3938,184 +4069,142 @@
       <c r="L42" t="s">
         <v>295</v>
       </c>
-      <c r="M42" t="s">
-        <v>296</v>
-      </c>
-      <c r="N42" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G43" s="21" t="s">
-        <v>375</v>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G43" s="14" t="s">
+        <v>372</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>366</v>
-      </c>
-      <c r="J43" t="s">
-        <v>300</v>
+        <v>363</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>300</v>
-      </c>
-      <c r="L43" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" t="s">
-        <v>376</v>
-      </c>
-      <c r="N43" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G44" s="21" t="s">
-        <v>365</v>
+        <v>373</v>
+      </c>
+      <c r="L43" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G44" s="14" t="s">
+        <v>362</v>
       </c>
       <c r="H44">
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>349</v>
-      </c>
-      <c r="J44" t="s">
-        <v>300</v>
+        <v>346</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>300</v>
-      </c>
-      <c r="L44" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" t="s">
-        <v>300</v>
-      </c>
-      <c r="N44" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G45" s="21" t="s">
-        <v>377</v>
+        <v>298</v>
+      </c>
+      <c r="L44" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G45" s="14" t="s">
+        <v>374</v>
       </c>
       <c r="H45">
         <v>3</v>
       </c>
       <c r="I45" t="s">
-        <v>325</v>
-      </c>
-      <c r="J45" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>304</v>
-      </c>
-      <c r="L45" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" t="s">
-        <v>300</v>
-      </c>
-      <c r="N45" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L45" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G46" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H46">
         <v>4</v>
       </c>
       <c r="I46" t="s">
-        <v>371</v>
-      </c>
-      <c r="J46" t="s">
-        <v>300</v>
+        <v>368</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>304</v>
-      </c>
-      <c r="L46" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46" t="s">
-        <v>300</v>
-      </c>
-      <c r="N46" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L46" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G47" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H47">
         <v>5</v>
       </c>
       <c r="I47" t="s">
-        <v>373</v>
-      </c>
-      <c r="J47" t="s">
-        <v>300</v>
+        <v>370</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>300</v>
-      </c>
-      <c r="L47" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" t="s">
-        <v>300</v>
-      </c>
-      <c r="N47" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L47" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G48" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H48">
         <v>6</v>
       </c>
       <c r="I48" t="s">
-        <v>373</v>
-      </c>
-      <c r="J48" t="s">
-        <v>300</v>
+        <v>370</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>300</v>
-      </c>
-      <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" t="s">
-        <v>300</v>
-      </c>
-      <c r="N48" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="L48" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="C49" t="s">
+        <v>376</v>
+      </c>
+      <c r="D49" t="s">
         <v>378</v>
       </c>
-      <c r="C49" t="s">
+      <c r="E49" t="s">
         <v>379</v>
       </c>
-      <c r="D49" t="s">
-        <v>381</v>
-      </c>
-      <c r="E49" t="s">
-        <v>382</v>
-      </c>
       <c r="F49" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G49" t="s">
         <v>290</v>
@@ -4135,178 +4224,172 @@
       <c r="L49" t="s">
         <v>295</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M49" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="N49" t="s">
+        <v>427</v>
+      </c>
+      <c r="O49" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>377</v>
+      </c>
+      <c r="G50" t="s">
+        <v>383</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>297</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>299</v>
+      </c>
+      <c r="L50" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G51" s="12" t="s">
         <v>296</v>
-      </c>
-      <c r="N49" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C50" t="s">
-        <v>380</v>
-      </c>
-      <c r="G50" t="s">
-        <v>386</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>299</v>
-      </c>
-      <c r="J50" t="s">
-        <v>300</v>
-      </c>
-      <c r="K50" t="s">
-        <v>300</v>
-      </c>
-      <c r="L50" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" t="s">
-        <v>301</v>
-      </c>
-      <c r="N50" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G51" t="s">
-        <v>298</v>
       </c>
       <c r="H51">
         <v>2</v>
       </c>
       <c r="I51" t="s">
-        <v>299</v>
-      </c>
-      <c r="J51" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>300</v>
-      </c>
-      <c r="L51" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" t="s">
-        <v>300</v>
+        <v>298</v>
+      </c>
+      <c r="L51" t="s">
+        <v>298</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>430</v>
       </c>
       <c r="N51" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G52" t="s">
-        <v>355</v>
+        <v>427</v>
+      </c>
+      <c r="O51" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G52" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="H52">
         <v>3</v>
       </c>
       <c r="I52" t="s">
-        <v>299</v>
-      </c>
-      <c r="J52" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>300</v>
-      </c>
-      <c r="L52" t="b">
-        <v>1</v>
-      </c>
-      <c r="M52" t="s">
-        <v>300</v>
-      </c>
-      <c r="N52" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G53" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H53">
         <v>4</v>
       </c>
       <c r="I53" t="s">
-        <v>320</v>
-      </c>
-      <c r="J53" t="s">
-        <v>300</v>
+        <v>317</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>300</v>
-      </c>
-      <c r="L53" t="b">
-        <v>1</v>
-      </c>
-      <c r="M53" t="s">
-        <v>322</v>
+        <v>319</v>
+      </c>
+      <c r="L53" t="s">
+        <v>298</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>430</v>
       </c>
       <c r="N53" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="O53" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G54" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H54">
         <v>5</v>
       </c>
       <c r="I54" t="s">
-        <v>349</v>
-      </c>
-      <c r="J54" t="s">
-        <v>300</v>
-      </c>
-      <c r="K54" t="s">
-        <v>300</v>
-      </c>
-      <c r="L54" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54">
+        <v>346</v>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54">
         <v>0</v>
       </c>
-      <c r="N54" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L54" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G55" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H55">
         <v>6</v>
       </c>
       <c r="I55" t="s">
-        <v>349</v>
-      </c>
-      <c r="J55" t="s">
-        <v>300</v>
-      </c>
-      <c r="K55" t="s">
-        <v>300</v>
-      </c>
-      <c r="L55" t="b">
-        <v>1</v>
-      </c>
-      <c r="M55">
+        <v>346</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55">
         <v>0</v>
       </c>
-      <c r="N55" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L55" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F56" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G56" t="s">
         <v>290</v>
@@ -4326,123 +4409,93 @@
       <c r="L56" t="s">
         <v>295</v>
       </c>
-      <c r="M56" t="s">
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>383</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>297</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>299</v>
+      </c>
+      <c r="L57" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
         <v>296</v>
-      </c>
-      <c r="N56" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G57" t="s">
-        <v>386</v>
-      </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57" t="s">
-        <v>299</v>
-      </c>
-      <c r="J57" t="s">
-        <v>300</v>
-      </c>
-      <c r="K57" t="s">
-        <v>300</v>
-      </c>
-      <c r="L57" t="b">
-        <v>1</v>
-      </c>
-      <c r="M57" t="s">
-        <v>301</v>
-      </c>
-      <c r="N57" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G58" t="s">
-        <v>298</v>
       </c>
       <c r="H58">
         <v>2</v>
       </c>
       <c r="I58" t="s">
-        <v>299</v>
-      </c>
-      <c r="J58" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>300</v>
-      </c>
-      <c r="L58" t="b">
-        <v>1</v>
-      </c>
-      <c r="M58" t="s">
-        <v>300</v>
-      </c>
-      <c r="N58" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L58" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G59" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H59">
         <v>3</v>
       </c>
       <c r="I59" t="s">
-        <v>392</v>
-      </c>
-      <c r="J59" t="s">
-        <v>300</v>
+        <v>389</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>304</v>
-      </c>
-      <c r="L59" t="b">
-        <v>1</v>
-      </c>
-      <c r="M59" t="s">
-        <v>300</v>
-      </c>
-      <c r="N59" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L59" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G60" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H60">
         <v>4</v>
       </c>
       <c r="I60" t="s">
-        <v>320</v>
-      </c>
-      <c r="J60" t="s">
-        <v>300</v>
+        <v>317</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>300</v>
-      </c>
-      <c r="L60" t="b">
-        <v>1</v>
-      </c>
-      <c r="M60" t="s">
-        <v>322</v>
-      </c>
-      <c r="N60" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="L60" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F61" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G61" t="s">
         <v>290</v>
@@ -4462,149 +4515,113 @@
       <c r="L61" t="s">
         <v>295</v>
       </c>
-      <c r="M61" t="s">
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G62" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>297</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>299</v>
+      </c>
+      <c r="L62" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G63" s="12" t="s">
         <v>296</v>
-      </c>
-      <c r="N61" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G62" t="s">
-        <v>386</v>
-      </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
-      <c r="I62" t="s">
-        <v>299</v>
-      </c>
-      <c r="J62" t="s">
-        <v>300</v>
-      </c>
-      <c r="K62" t="s">
-        <v>300</v>
-      </c>
-      <c r="L62" t="b">
-        <v>1</v>
-      </c>
-      <c r="M62" t="s">
-        <v>301</v>
-      </c>
-      <c r="N62" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G63" t="s">
-        <v>298</v>
       </c>
       <c r="H63">
         <v>2</v>
       </c>
       <c r="I63" t="s">
-        <v>299</v>
-      </c>
-      <c r="J63" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>300</v>
-      </c>
-      <c r="L63" t="b">
-        <v>1</v>
-      </c>
-      <c r="M63" t="s">
-        <v>300</v>
-      </c>
-      <c r="N63" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G64" t="s">
-        <v>365</v>
+        <v>298</v>
+      </c>
+      <c r="L63" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G64" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="H64">
         <v>3</v>
       </c>
       <c r="I64" t="s">
-        <v>349</v>
-      </c>
-      <c r="J64" t="s">
-        <v>300</v>
+        <v>346</v>
+      </c>
+      <c r="J64" t="b">
+        <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>300</v>
-      </c>
-      <c r="L64" t="b">
-        <v>1</v>
-      </c>
-      <c r="M64" t="s">
-        <v>300</v>
-      </c>
-      <c r="N64" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="65" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="G65" t="s">
-        <v>375</v>
+        <v>298</v>
+      </c>
+      <c r="L64" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G65" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="H65">
         <v>4</v>
       </c>
       <c r="I65" t="s">
-        <v>349</v>
-      </c>
-      <c r="J65" t="s">
-        <v>300</v>
+        <v>346</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>300</v>
-      </c>
-      <c r="L65" t="b">
-        <v>1</v>
-      </c>
-      <c r="M65" t="s">
-        <v>300</v>
-      </c>
-      <c r="N65" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="66" spans="5:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L65" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G66" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H66">
         <v>5</v>
       </c>
       <c r="I66" t="s">
-        <v>320</v>
-      </c>
-      <c r="J66" t="s">
-        <v>300</v>
+        <v>317</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>300</v>
-      </c>
-      <c r="L66" t="b">
-        <v>1</v>
-      </c>
-      <c r="M66" t="s">
-        <v>322</v>
-      </c>
-      <c r="N66" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" spans="5:14" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="L66" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E67" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F67" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G67" t="s">
         <v>290</v>
@@ -4624,219 +4641,283 @@
       <c r="L67" t="s">
         <v>295</v>
       </c>
-      <c r="M67" t="s">
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>383</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>297</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="s">
+        <v>299</v>
+      </c>
+      <c r="L68" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
         <v>296</v>
-      </c>
-      <c r="N67" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="G68" t="s">
-        <v>386</v>
-      </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68" t="s">
-        <v>299</v>
-      </c>
-      <c r="J68" t="s">
-        <v>300</v>
-      </c>
-      <c r="K68" t="s">
-        <v>300</v>
-      </c>
-      <c r="L68" t="b">
-        <v>1</v>
-      </c>
-      <c r="M68" t="s">
-        <v>301</v>
-      </c>
-      <c r="N68" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="69" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="G69" t="s">
-        <v>298</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69" t="s">
-        <v>299</v>
-      </c>
-      <c r="J69" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>300</v>
-      </c>
-      <c r="L69" t="b">
-        <v>1</v>
-      </c>
-      <c r="M69" t="s">
-        <v>300</v>
-      </c>
-      <c r="N69" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="70" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="G70" t="s">
-        <v>365</v>
+        <v>298</v>
+      </c>
+      <c r="L69" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G70" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="H70">
         <v>3</v>
       </c>
       <c r="I70" t="s">
-        <v>349</v>
-      </c>
-      <c r="J70" t="s">
-        <v>300</v>
+        <v>346</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>300</v>
-      </c>
-      <c r="L70" t="b">
-        <v>1</v>
-      </c>
-      <c r="M70" t="s">
-        <v>300</v>
-      </c>
-      <c r="N70" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="71" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="G71" t="s">
-        <v>375</v>
+        <v>298</v>
+      </c>
+      <c r="L70" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G71" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="H71">
         <v>4</v>
       </c>
       <c r="I71" t="s">
-        <v>349</v>
-      </c>
-      <c r="J71" t="s">
-        <v>300</v>
+        <v>346</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>300</v>
-      </c>
-      <c r="L71" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" t="s">
-        <v>300</v>
-      </c>
-      <c r="N71" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="72" spans="5:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L71" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G72" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H72">
         <v>5</v>
       </c>
       <c r="I72" t="s">
-        <v>328</v>
-      </c>
-      <c r="J72" t="s">
-        <v>300</v>
+        <v>325</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>304</v>
-      </c>
-      <c r="L72" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72" t="s">
-        <v>300</v>
-      </c>
-      <c r="N72" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="73" spans="5:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L72" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G73" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H73">
         <v>6</v>
       </c>
       <c r="I73" t="s">
-        <v>325</v>
-      </c>
-      <c r="J73" t="s">
-        <v>300</v>
+        <v>322</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>304</v>
-      </c>
-      <c r="L73" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73" t="s">
-        <v>300</v>
-      </c>
-      <c r="N73" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="74" spans="5:14" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="L73" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G74" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H74">
         <v>7</v>
       </c>
       <c r="I74" t="s">
+        <v>317</v>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
+      </c>
+      <c r="K74" t="s">
+        <v>319</v>
+      </c>
+      <c r="L74" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G75" t="s">
         <v>320</v>
-      </c>
-      <c r="J74" t="s">
-        <v>300</v>
-      </c>
-      <c r="K74" t="s">
-        <v>300</v>
-      </c>
-      <c r="L74" t="b">
-        <v>1</v>
-      </c>
-      <c r="M74" t="s">
-        <v>322</v>
-      </c>
-      <c r="N74" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="75" spans="5:14" x14ac:dyDescent="0.25">
-      <c r="G75" t="s">
-        <v>323</v>
       </c>
       <c r="H75">
         <v>8</v>
       </c>
       <c r="I75" t="s">
+        <v>317</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>319</v>
+      </c>
+      <c r="L75" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B77" t="s">
+        <v>330</v>
+      </c>
+      <c r="C77" t="s">
+        <v>423</v>
+      </c>
+      <c r="F77" t="s">
+        <v>416</v>
+      </c>
+      <c r="G77" t="s">
+        <v>290</v>
+      </c>
+      <c r="H77" t="s">
+        <v>291</v>
+      </c>
+      <c r="I77" t="s">
+        <v>292</v>
+      </c>
+      <c r="J77" t="s">
+        <v>293</v>
+      </c>
+      <c r="K77" t="s">
+        <v>294</v>
+      </c>
+      <c r="L77" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>424</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="H78" s="23">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>297</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
+      </c>
+      <c r="K78" t="s">
+        <v>298</v>
+      </c>
+      <c r="L78" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>425</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="H79" s="23">
+        <v>2</v>
+      </c>
+      <c r="I79" t="s">
+        <v>389</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
+      <c r="K79" t="s">
+        <v>298</v>
+      </c>
+      <c r="L79" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G80" t="s">
+        <v>318</v>
+      </c>
+      <c r="H80">
+        <v>3</v>
+      </c>
+      <c r="I80" t="s">
+        <v>317</v>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
+      </c>
+      <c r="K80" t="s">
+        <v>319</v>
+      </c>
+      <c r="L80" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="81" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="G81" t="s">
         <v>320</v>
       </c>
-      <c r="J75" t="s">
-        <v>300</v>
-      </c>
-      <c r="K75" t="s">
-        <v>300</v>
-      </c>
-      <c r="L75" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75" t="s">
-        <v>322</v>
-      </c>
-      <c r="N75" t="s">
-        <v>300</v>
+      <c r="H81">
+        <v>4</v>
+      </c>
+      <c r="I81" t="s">
+        <v>317</v>
+      </c>
+      <c r="J81" t="b">
+        <v>1</v>
+      </c>
+      <c r="K81" t="s">
+        <v>319</v>
+      </c>
+      <c r="L81" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4846,6 +4927,225 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B56876D-4C06-431E-B583-CAE827E1B1A6}">
+  <dimension ref="B3:C28"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="C6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="C8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="C9" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>398</v>
+      </c>
+      <c r="C11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="C13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="C14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>404</v>
+      </c>
+      <c r="C17" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C18" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>408</v>
+      </c>
+      <c r="C19" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="C20" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="C22" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>413</v>
+      </c>
+      <c r="C23" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>415</v>
+      </c>
+      <c r="C24" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="C25" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C26" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>419</v>
+      </c>
+      <c r="C27" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>421</v>
+      </c>
+      <c r="C28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0748038D-1236-4988-927E-F84C4BE6FB57}">
   <dimension ref="B2:H25"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -4859,16 +5159,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="F2" s="10" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="F2" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -5083,11 +5383,11 @@
       <c r="D14" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
@@ -5311,7 +5611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E20354BF-4F84-4E95-A339-0261BEB602AA}">
   <dimension ref="B2:D7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5322,11 +5622,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -5392,7 +5692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2628166-061C-4CD1-8E17-220D45A512C7}">
   <dimension ref="B2:D12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5403,11 +5703,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -5528,7 +5828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAB157D-DAD5-4469-B47A-8F1B8BB5E87F}">
   <dimension ref="B2:D10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5539,11 +5839,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -5579,11 +5879,11 @@
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -5628,7 +5928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1B5E7C-69C2-4771-ACE8-8F429CDFDDC0}">
   <dimension ref="B2:D19"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5639,11 +5939,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -5841,7 +6141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC1774E-773F-4BF5-B419-73A866990E01}">
   <dimension ref="B2:D31"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5852,11 +6152,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -6001,11 +6301,11 @@
       <c r="D17" s="2"/>
     </row>
     <row r="19" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -6126,214 +6426,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E56573-585C-4CF5-B8A4-057305F06120}">
-  <dimension ref="B2:D23"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B11:D11"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/note/tables.xlsx
+++ b/note/tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SamaSama\note\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0916B686-C30C-47C3-B946-D7B00D5A0967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539E9797-C5D8-427D-939F-F7D6CF654D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1529,7 +1529,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1578,6 +1578,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1591,7 +1597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1628,6 +1634,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1646,8 +1654,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1940,16 +1947,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="F2" s="17" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="F2" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -2032,11 +2039,11 @@
       <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -2119,11 +2126,11 @@
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
@@ -2177,11 +2184,11 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
       <c r="F16" s="8" t="s">
         <v>76</v>
       </c>
@@ -2350,11 +2357,11 @@
       <c r="D25" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
@@ -2505,11 +2512,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2567,11 +2574,11 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
@@ -2715,11 +2722,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
@@ -2873,11 +2880,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -2987,11 +2994,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -3178,11 +3185,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -3289,7 +3296,7 @@
       <c r="G3" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="17">
         <v>1</v>
       </c>
       <c r="I3" t="s">
@@ -3309,7 +3316,7 @@
       <c r="G4" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="17">
         <v>2</v>
       </c>
       <c r="I4" t="s">
@@ -3506,82 +3513,82 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
+      <c r="G14" s="24" t="s">
         <v>321</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="24">
         <v>12</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="J14" t="b">
+      <c r="J14" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="K14" t="s">
-        <v>298</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="K14" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="L14" s="24" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G15" t="s">
+      <c r="G15" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="24">
         <v>13</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="J15" t="b">
+      <c r="J15" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="K15" t="s">
-        <v>298</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="K15" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="L15" s="24" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G16" t="s">
+      <c r="G16" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="24">
         <v>14</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="J16" t="b">
+      <c r="J16" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="K16" t="s">
-        <v>298</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="K16" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="L16" s="24" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G17" t="s">
+      <c r="G17" s="24" t="s">
         <v>326</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="24">
         <v>15</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="J17" t="b">
+      <c r="J17" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="K17" t="s">
-        <v>298</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="K17" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="L17" s="24" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4331,7 +4338,7 @@
       <c r="L53" t="s">
         <v>298</v>
       </c>
-      <c r="M53" s="23" t="s">
+      <c r="M53" s="17" t="s">
         <v>430</v>
       </c>
       <c r="N53" t="s">
@@ -4841,7 +4848,7 @@
       <c r="G78" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="H78" s="23">
+      <c r="H78" s="17">
         <v>1</v>
       </c>
       <c r="I78" t="s">
@@ -4864,7 +4871,7 @@
       <c r="G79" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="H79" s="23">
+      <c r="H79" s="17">
         <v>2</v>
       </c>
       <c r="I79" t="s">
@@ -4956,7 +4963,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="16" t="s">
         <v>391</v>
       </c>
       <c r="C6" t="s">
@@ -4964,7 +4971,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>390</v>
       </c>
       <c r="C7" t="s">
@@ -4972,7 +4979,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="16" t="s">
         <v>386</v>
       </c>
       <c r="C8" t="s">
@@ -4980,7 +4987,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="16" t="s">
         <v>387</v>
       </c>
       <c r="C9" t="s">
@@ -5012,7 +5019,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>360</v>
       </c>
       <c r="C13" t="s">
@@ -5020,7 +5027,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="16" t="s">
         <v>361</v>
       </c>
       <c r="C14" t="s">
@@ -5068,7 +5075,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="16" t="s">
         <v>338</v>
       </c>
       <c r="C20" t="s">
@@ -5076,7 +5083,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="16" t="s">
         <v>340</v>
       </c>
       <c r="C21" t="s">
@@ -5084,7 +5091,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="16" t="s">
         <v>339</v>
       </c>
       <c r="C22" t="s">
@@ -5108,7 +5115,7 @@
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="16" t="s">
         <v>416</v>
       </c>
       <c r="C25" t="s">
@@ -5116,7 +5123,7 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="16" t="s">
         <v>417</v>
       </c>
       <c r="C26" t="s">
@@ -5159,16 +5166,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="F2" s="20" t="s">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="F2" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -5383,11 +5390,11 @@
       <c r="D14" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
@@ -5622,11 +5629,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -5703,11 +5710,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -5839,11 +5846,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -5879,11 +5886,11 @@
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -5939,11 +5946,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -6152,11 +6159,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -6301,11 +6308,11 @@
       <c r="D17" s="2"/>
     </row>
     <row r="19" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
